--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20222.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="35">
   <si>
     <t>Mat</t>
   </si>
@@ -85,19 +85,13 @@
     <t>FLORES</t>
   </si>
   <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>CAMACHO</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>DE JESUS</t>
+    <t>CRUZ</t>
   </si>
   <si>
     <t>LUGO</t>
@@ -106,22 +100,13 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>MEZA</t>
-  </si>
-  <si>
     <t>SALAS</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
-    <t>RICO</t>
+    <t>GUZMAN</t>
   </si>
   <si>
     <t>ZAYRA</t>
@@ -130,22 +115,13 @@
     <t>XIMENA</t>
   </si>
   <si>
-    <t>KEVIN</t>
-  </si>
-  <si>
-    <t>ACSA FERNANDA</t>
-  </si>
-  <si>
     <t>MELISA VIANNEY</t>
   </si>
   <si>
-    <t>GUADALUPE</t>
-  </si>
-  <si>
     <t>ILEANA</t>
   </si>
   <si>
-    <t>FRANCISCO EMMANUEL</t>
+    <t>KARENT LILIANA</t>
   </si>
 </sst>
 </file>
@@ -689,16 +665,19 @@
         <v>43</v>
       </c>
       <c r="D2">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>86.05</v>
+      </c>
+      <c r="H2">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -712,16 +691,19 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>71.43000000000001</v>
+      </c>
+      <c r="H3">
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -735,16 +717,19 @@
         <v>42</v>
       </c>
       <c r="D4">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>97.62</v>
+      </c>
+      <c r="H4">
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -758,16 +743,19 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>92.68000000000001</v>
+      </c>
+      <c r="H5">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -832,7 +820,7 @@
         <v>86.05</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -849,16 +837,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>73.81</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -875,16 +863,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4">
-        <v>95.23999999999999</v>
+        <v>97.62</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -910,7 +898,7 @@
         <v>92.68000000000001</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -920,7 +908,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -958,10 +946,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -981,10 +969,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -998,16 +986,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920354</v>
+        <v>22330051920145</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1021,39 +1009,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920144</v>
+        <v>22330051920114</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920145</v>
+        <v>22330051920128</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1062,75 +1050,6 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920087</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920114</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>19330051920155</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20222.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="32">
   <si>
     <t>Mat</t>
   </si>
@@ -79,43 +79,34 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>LUGO</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
     <t>GUZMAN</t>
   </si>
   <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
     <t>ZAYRA</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>MELISA VIANNEY</t>
   </si>
   <si>
     <t>ILEANA</t>
@@ -908,7 +899,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -940,16 +931,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920100</v>
+        <v>22330051920340</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -963,22 +954,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920132</v>
+        <v>22330051920100</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -986,70 +977,47 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920145</v>
+        <v>22330051920114</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920114</v>
+        <v>22330051920128</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920128</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20222.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -82,9 +82,6 @@
     <t>LARRACILLA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
@@ -94,9 +91,6 @@
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>LUGO</t>
-  </si>
-  <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
@@ -104,9 +98,6 @@
   </si>
   <si>
     <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>ZAYRA</t>
   </si>
   <si>
     <t>ILEANA</t>
@@ -899,7 +890,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -937,10 +928,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -954,16 +945,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920100</v>
+        <v>22330051920114</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -972,52 +963,29 @@
         <v>10</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920114</v>
+        <v>22330051920128</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920128</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20222.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -77,33 +77,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>LARRACILLA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>GUZMAN</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>ILEANA</t>
-  </si>
-  <si>
-    <t>KARENT LILIANA</t>
   </si>
 </sst>
 </file>
@@ -793,16 +766,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G2">
-        <v>86.05</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -819,16 +792,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>71.43000000000001</v>
+        <v>80.95</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -890,7 +863,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -920,75 +893,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920340</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920114</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920128</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Caballero Rosas María Teresa - Estadisticos 20222.xlsx
+++ b/docentes/Caballero Rosas María Teresa - Estadisticos 20222.xlsx
@@ -818,16 +818,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>97.62</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -844,16 +844,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>92.68000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
